--- a/dist/template/site_machine_template.xlsx
+++ b/dist/template/site_machine_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29920" windowHeight="12960"/>
+    <workbookView windowWidth="30240" windowHeight="13280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>下架日期</t>
   </si>
@@ -44,10 +44,13 @@
     <t>备注</t>
   </si>
   <si>
-    <t>S19XP  257T</t>
+    <t>S19XP  134T</t>
   </si>
   <si>
     <t>NGSBEEABCJDAA02JZ</t>
+  </si>
+  <si>
+    <t>板1无算力</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1072,9 @@
       <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" s="5">
         <v>30.119</v>
       </c>

--- a/dist/template/site_machine_template.xlsx
+++ b/dist/template/site_machine_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13280"/>
+    <workbookView windowWidth="29940" windowHeight="12980"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>45809</v>
+        <v>45816</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
